--- a/artfynd/A 60741-2023 artfynd.xlsx
+++ b/artfynd/A 60741-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60741-2023 artfynd.xlsx
+++ b/artfynd/A 60741-2023 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66538687</v>
+        <v>116486769</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, Vrm</t>
+          <t>Byxetjärnen, Byxetjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344791.9964018451</v>
+        <v>344785</v>
       </c>
       <c r="R2" t="n">
-        <v>6604316.464916003</v>
+        <v>6604316</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,39 +767,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>21474</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116486769</v>
+        <v>116486888</v>
       </c>
       <c r="B3" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -828,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Byxetjärnen (Byxetjärnen), Vrm</t>
+          <t>Byxetjärnen, Byxetjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344785</v>
+        <v>344752</v>
       </c>
       <c r="R3" t="n">
-        <v>6604316</v>
+        <v>6604306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116486888</v>
+        <v>66538687</v>
       </c>
       <c r="B4" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Byxetjärnen (Byxetjärnen), Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344752</v>
+        <v>344792</v>
       </c>
       <c r="R4" t="n">
-        <v>6604306</v>
+        <v>6604316</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,15 +971,20 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>21474</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
